--- a/dietitian_forms/017_daily_consumption_report_form--dietitian_forms.xlsx
+++ b/dietitian_forms/017_daily_consumption_report_form--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What did you eat today?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe your food consumption</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,10 +555,14 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -574,10 +582,14 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HH -MM AM/PM</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -597,7 +609,11 @@
           <t>Consumption Amount</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Number of units or amount</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -620,7 +636,11 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Additional notes about today's consumption</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -643,7 +663,11 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Phone number or extension</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -666,7 +690,11 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Email address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -689,7 +717,11 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select category for this consumption</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -712,7 +744,11 @@
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select subcategories for this consumption</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -735,7 +771,11 @@
           <t>Submit</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Submit this form</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -758,7 +798,11 @@
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cancel this form</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -781,7 +825,11 @@
           <t>Back</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Back to previous page</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -804,7 +852,11 @@
           <t>Save</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Save this form</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -827,261 +879,12 @@
           <t>Reset</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reset this form</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Cancel</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Back</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Save</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Reset</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +934,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>category_1</t>
+          <t>fresh_fruits</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Category 1</t>
+          <t>Fresh Fruits</t>
         </is>
       </c>
     </row>
@@ -1148,12 +951,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>category_2</t>
+          <t>cooked_food</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Category 2</t>
+          <t>Cooked Food</t>
         </is>
       </c>
     </row>
@@ -1165,29 +968,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>category_3</t>
+          <t>snacks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Category 3</t>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>subcat_1</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Subcat 1</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1002,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>subcat_2</t>
+          <t>fresh_fruits</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Subcat 2</t>
+          <t>Fresh Fruits</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1019,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>subcat_3</t>
+          <t>cooked_food</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Subcat 3</t>
+          <t>Cooked Food</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>desserts</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Desserts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>beverages</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Beverages</t>
         </is>
       </c>
     </row>
